--- a/JsonConverter/ExcelFiles/Tutorial.xlsx
+++ b/JsonConverter/ExcelFiles/Tutorial.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="138">
   <si>
     <t xml:space="preserve">퀘스트 ID</t>
   </si>
@@ -94,26 +94,7 @@
     <t xml:space="preserve">TycoonEnter</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="&quot;맑은 고딕&quot;"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TutorialImage/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="&quot;맑은 고딕&quot;"/>
-        <family val="0"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">Tutorial_01_01</t>
-    </r>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_01_01</t>
   </si>
   <si>
     <t xml:space="preserve">Tutorial_01_02</t>
@@ -123,6 +104,9 @@
   </si>
   <si>
     <t xml:space="preserve">화면 우측 최상단 버튼으로 오늘의 업무(퀘스트)를 확인할 수 있습니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_01_02</t>
   </si>
   <si>
     <t xml:space="preserve">Tutorial_01_03</t>
@@ -153,6 +137,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_01_03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_01_04</t>
   </si>
   <si>
@@ -162,6 +149,9 @@
     <t xml:space="preserve">원하는 방을 클릭하면 커서를 흰색 건축영역으로 이동하면 방이 차지하는 공간만큼 청사진이 나타납니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_01_04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_01_05</t>
   </si>
   <si>
@@ -169,6 +159,9 @@
   </si>
   <si>
     <t xml:space="preserve">원하는 위치에 클릭을 하여 금액을 지불하고 건설합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_01_05</t>
   </si>
   <si>
     <r>
@@ -208,6 +201,9 @@
     <t xml:space="preserve">Quest_01_02</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_02</t>
   </si>
   <si>
@@ -217,6 +213,9 @@
     <t xml:space="preserve">사무실 내에는 여러가지 상호작용이 가능합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_03</t>
   </si>
   <si>
@@ -226,6 +225,9 @@
     <t xml:space="preserve">사무실 내 쇼핑카트를 클릭하면 상점 창으로 이동합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_04</t>
   </si>
   <si>
@@ -235,6 +237,9 @@
     <t xml:space="preserve">사무실 내 서류를 클릭하면 영입 가능한 영웅의 목록을 볼 수 있으며 영입하기를 통해 시설 입소가 가능합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_05</t>
   </si>
   <si>
@@ -244,6 +249,9 @@
     <t xml:space="preserve">사무실 내 모래시계를 클릭하면 하루가 지나가며 정산을 합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_06</t>
   </si>
   <si>
@@ -251,6 +259,9 @@
   </si>
   <si>
     <t xml:space="preserve">사무실 내 문을 클릭하면 타이쿤 화면으로 나갑니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_06</t>
   </si>
   <si>
     <t xml:space="preserve">Tutorial_03_07</t>
@@ -263,6 +274,9 @@
 사무실 내 서류를 클릭하고, 원하는 영웅을 클릭합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_03_08</t>
   </si>
   <si>
@@ -270,6 +284,9 @@
   </si>
   <si>
     <t xml:space="preserve">타이쿤 화면에서 푸른색으로 활성화된 비어있는 침실에 배치합니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_03_08</t>
   </si>
   <si>
     <r>
@@ -306,6 +323,9 @@
     <t xml:space="preserve">Quest_01_03</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_05_01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_05_02</t>
   </si>
   <si>
@@ -315,6 +335,9 @@
     <t xml:space="preserve">휴식, 수면, 운동 등 원하는 활동을 클릭하고 좌측 시간을 클릭하면 일정을 배정할 수 있습니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_05_02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_05_03</t>
   </si>
   <si>
@@ -324,6 +347,9 @@
     <t xml:space="preserve">배정된 일정을 수행하려면 알맞은 방의 설치가 필요합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_05_03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_05_04</t>
   </si>
   <si>
@@ -331,6 +357,9 @@
   </si>
   <si>
     <t xml:space="preserve">일정에 맞는 방이 없을 경우 환자의 만족도가 하락합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_05_04</t>
   </si>
   <si>
     <r>
@@ -367,6 +396,9 @@
     <t xml:space="preserve">Quest_01_04</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_06_01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_06_02</t>
   </si>
   <si>
@@ -374,6 +406,9 @@
   </si>
   <si>
     <t xml:space="preserve">전체 평가 등급 D를 2일 이상 받으면 게임오버가 됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_06_02</t>
   </si>
   <si>
     <r>
@@ -410,6 +445,9 @@
     <t xml:space="preserve">Quest_01_05</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_01</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_02</t>
   </si>
   <si>
@@ -419,6 +457,9 @@
     <t xml:space="preserve">입소한 환자들의 명단 중 가상 전투에 내보내길 원하는 3명을 클릭하고 확인 합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_03</t>
   </si>
   <si>
@@ -428,6 +469,9 @@
     <t xml:space="preserve">전투는 자동으로 진행되며 속도 수치에 따라 행동 순서가 결정됩니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_04</t>
   </si>
   <si>
@@ -437,6 +481,9 @@
     <t xml:space="preserve">플레이어는 전투 훈련 중에 개입을 할 수 있습니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_04</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_05</t>
   </si>
   <si>
@@ -446,6 +493,9 @@
     <t xml:space="preserve">지원하기 – 도구를 사용하여 지원하여 상태이상을 제거합니다. 에너지를 1 소모합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_05</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_06</t>
   </si>
   <si>
@@ -455,6 +505,9 @@
     <t xml:space="preserve">회복하기 – 아이템를 사용하여 체력을 회복합니다. 에너지를 2 소모합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_06</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_07</t>
   </si>
   <si>
@@ -464,6 +517,9 @@
     <t xml:space="preserve">영웅변경 – 대기중인 다른 영웅으로 교체할 수 있습니다.에너지를 2을 소모합니다</t>
   </si>
   <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tutorial_07_08</t>
   </si>
   <si>
@@ -471,6 +527,9 @@
   </si>
   <si>
     <t xml:space="preserve">턴 종료 – 턴을 넘기려면 턴 종료 버튼을 누릅니다. 대기열에 따라 자동 전투가 진행됩니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image/Tutorial/Tutorial_07_08</t>
   </si>
 </sst>
 </file>
@@ -544,14 +603,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
+      <name val="나눔고딕"/>
       <family val="0"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="나눔고딕"/>
+      <name val="&quot;맑은 고딕&quot;"/>
       <family val="0"/>
       <charset val="129"/>
     </font>
@@ -617,7 +676,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -670,6 +729,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -678,7 +741,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -686,7 +749,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -702,7 +765,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1087,23 +1150,23 @@
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="13"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="13"/>
-      <c r="V4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -1112,10 +1175,10 @@
       <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="12"/>
@@ -1123,756 +1186,808 @@
       <c r="G5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="13"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="13"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="14"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="13"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>33</v>
+      <c r="C7" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>35</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="13"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>36</v>
+      <c r="C8" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="13"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="13"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>45</v>
+        <v>49</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>50</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="13"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3"/>
       <c r="G11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="13"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="13"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>54</v>
+        <v>61</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="13"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="13"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="13"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>63</v>
+        <v>73</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="13"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" s="13"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>71</v>
+        <v>83</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>84</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="13"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>74</v>
+        <v>87</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>88</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="13"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>77</v>
+        <v>91</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="13"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>81</v>
+        <v>96</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>97</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="13"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>85</v>
+        <v>101</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="13"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="13"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>89</v>
+        <v>106</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="13"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>93</v>
+        <v>111</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>112</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="13"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>96</v>
+        <v>115</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>116</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="13"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>99</v>
+        <v>119</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="13"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>102</v>
+        <v>123</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>124</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="13"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>105</v>
+        <v>127</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>128</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="13"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>108</v>
+        <v>131</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="13"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>111</v>
+        <v>135</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" s="13"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="13"/>
+      <c r="K30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
@@ -1885,7 +2000,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="13"/>
+      <c r="K31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
@@ -1898,12 +2013,12 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="20"/>
+      <c r="K32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="13"/>
+      <c r="C33" s="14"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -1911,143 +2026,143 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="13"/>
+      <c r="K33" s="14"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="L34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="L34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="L35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="L37" s="13"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
